--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C0C23EB-2E99-4D04-B6F6-FEA2AEA6ED2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1596533-A2A5-4829-A63C-4077E8AC7E4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D1C12BC-E355-4CAA-A9B1-F74C52C87023}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF37682-E804-4FA7-84FE-C8D18C89C1FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF66B13-B537-43FB-ACC5-79125ECC5452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A50E53C-FD6B-41F6-8352-F7593F41B97A}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1596533-A2A5-4829-A63C-4077E8AC7E4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20EB8B75-26CA-4F61-A663-4C0F4D84E9C7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF37682-E804-4FA7-84FE-C8D18C89C1FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9901ADCE-1225-4157-8DCF-7A319558327B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A50E53C-FD6B-41F6-8352-F7593F41B97A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F487BEB3-A0EA-43FB-BB4E-8BE8F4C510B0}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20EB8B75-26CA-4F61-A663-4C0F4D84E9C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AD3B0DB-2EF6-40C7-85C3-9E24884AAF8E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9901ADCE-1225-4157-8DCF-7A319558327B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D3735B-FFE6-4A0E-83C4-9689BCA1F096}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F487BEB3-A0EA-43FB-BB4E-8BE8F4C510B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475C94A4-5D25-4931-AE65-2C7E35606CB1}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AD3B0DB-2EF6-40C7-85C3-9E24884AAF8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF738F1-500B-468E-AB71-73A1FA19A83E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8D3735B-FFE6-4A0E-83C4-9689BCA1F096}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5B60B0B-038E-41DA-9336-93FA9B898E18}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475C94A4-5D25-4931-AE65-2C7E35606CB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81D6886F-FA63-4648-B9A0-4713F082231A}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -12008,13 +12008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E6DE254-6FFE-496C-81A8-AF5988F5A877}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D23D710-1311-437F-A922-3154EA140D42}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ED1E5C3-C174-4285-810D-BF51F9743F3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CCFFB94-7502-43A2-A232-CE0242D7C187}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BC69BA0-ED8B-49DF-9570-920AF2CF4468}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0146A26B-CF66-4237-93A4-C0319C2F7A44}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -12008,13 +12008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D23D710-1311-437F-A922-3154EA140D42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07B5321F-8386-449D-B137-6331E044CFAB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CCFFB94-7502-43A2-A232-CE0242D7C187}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE59F913-853E-463E-BC35-996FABA7A17F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0146A26B-CF66-4237-93A4-C0319C2F7A44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C51C440-A079-411F-9B24-3F96F6BE528D}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -11730,291 +11730,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07B5321F-8386-449D-B137-6331E044CFAB}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE59F913-853E-463E-BC35-996FABA7A17F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C51C440-A079-411F-9B24-3F96F6BE528D}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -11730,4 +11730,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0384310-DCBB-401C-8EA0-AB56ECC9A616}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FB82663-7A12-4F8A-966D-5B23C42C5E85}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE07C13-31F2-484D-BCEB-F0F48AD5168E}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -11730,291 +11730,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0384310-DCBB-401C-8EA0-AB56ECC9A616}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FB82663-7A12-4F8A-966D-5B23C42C5E85}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE07C13-31F2-484D-BCEB-F0F48AD5168E}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -11730,4 +11730,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FD08900-9920-475B-9D89-98EE63EB7D7B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E05A6BBD-112B-4605-8E77-F98E11155E81}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9858EA8C-D58E-4F76-ADB9-6087D29126EE}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -12008,13 +12008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FD08900-9920-475B-9D89-98EE63EB7D7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E841CA-1F80-4399-8C0E-16E35AF694CF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E05A6BBD-112B-4605-8E77-F98E11155E81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59056D84-D8F1-4EED-B51B-C7EE54C4C67D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9858EA8C-D58E-4F76-ADB9-6087D29126EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF8BA179-0ED8-4772-8D60-B8248286D78D}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -12008,13 +12008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E841CA-1F80-4399-8C0E-16E35AF694CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4EC56FC-D67E-45C5-92ED-2D5D4F06D358}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59056D84-D8F1-4EED-B51B-C7EE54C4C67D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AD92C24-F8D0-4F73-9900-AFF239DA4A66}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF8BA179-0ED8-4772-8D60-B8248286D78D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669BED09-BA68-4A32-B7B7-1854D939AF56}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -12008,13 +12008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4EC56FC-D67E-45C5-92ED-2D5D4F06D358}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97CC218E-1E82-431E-B8E9-3548FF936233}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AD92C24-F8D0-4F73-9900-AFF239DA4A66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55A54A65-6860-4D63-A449-41A6BE396899}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{669BED09-BA68-4A32-B7B7-1854D939AF56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83F6C908-65E0-4152-AA20-3931ABE0BC25}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -12008,13 +12008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97CC218E-1E82-431E-B8E9-3548FF936233}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4BDDECE-6BCA-4EAD-AD1C-6F3ABE0B5F5B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55A54A65-6860-4D63-A449-41A6BE396899}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B58B51-C5E8-49D5-ACEF-BB79E6263C85}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83F6C908-65E0-4152-AA20-3931ABE0BC25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8244115-D284-43E9-AF9F-39643172E754}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -12008,13 +12008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4BDDECE-6BCA-4EAD-AD1C-6F3ABE0B5F5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BB92EF8-EDCD-4186-8C4C-1D6FEE259634}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B58B51-C5E8-49D5-ACEF-BB79E6263C85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCBFE6F1-4CB7-4992-8D85-ECB70D0F4CF7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8244115-D284-43E9-AF9F-39643172E754}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46E90952-079C-4749-9E74-B36A2FADED7B}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -11730,291 +11730,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BB92EF8-EDCD-4186-8C4C-1D6FEE259634}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCBFE6F1-4CB7-4992-8D85-ECB70D0F4CF7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46E90952-079C-4749-9E74-B36A2FADED7B}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -11730,4 +11730,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39321944-8028-486F-9081-A5E027C1D82F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBEB000E-35C8-4228-97F4-FE8A0B0D6DF1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69DB224B-2982-4F21-AE29-89448AC208DE}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -40686,13 +40686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B476C4BB-9C91-42D4-AB02-B8C50B66676D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BC2B6A7-2355-4F14-969B-6969F3E9692B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4644071-682C-4DCD-9CEF-14F18DD8B4B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2404E027-E37B-4231-A2D1-4D4335BF8D98}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F392C433-9020-4DEC-BB16-190A620D11BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA79C7B9-9BA9-4DAE-8068-FFF92011BF14}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -40686,13 +40686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BC2B6A7-2355-4F14-969B-6969F3E9692B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900FF713-76C1-4E39-9ECD-CFB3513523DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2404E027-E37B-4231-A2D1-4D4335BF8D98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CEF0DC3-8856-49B8-A23A-FCD7EEDF0D1F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA79C7B9-9BA9-4DAE-8068-FFF92011BF14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E66D3C9-85B4-4F06-A21F-71E2423F8847}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -40686,13 +40686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900FF713-76C1-4E39-9ECD-CFB3513523DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E0E3AE-81EB-43E9-B903-BDCBA679F3D5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CEF0DC3-8856-49B8-A23A-FCD7EEDF0D1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50C68ADB-0189-452A-B83A-F875652AA0FB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E66D3C9-85B4-4F06-A21F-71E2423F8847}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F0CC83-EDCF-47F2-BAD1-5B56107181CA}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -40686,13 +40686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25E0E3AE-81EB-43E9-B903-BDCBA679F3D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD173B35-9274-4C66-B95B-E33D16B66E1E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50C68ADB-0189-452A-B83A-F875652AA0FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5E6638D-6FD1-41BB-BA35-3B1688C1E326}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F0CC83-EDCF-47F2-BAD1-5B56107181CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{560E6CB0-4BB4-4898-8A8E-80E3AEE72D42}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4283" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4289" uniqueCount="771">
   <si>
     <t>species_sci</t>
   </si>
@@ -1952,6 +1952,9 @@
   </si>
   <si>
     <t>Panthera leo</t>
+  </si>
+  <si>
+    <t>Panthera tigris</t>
   </si>
   <si>
     <t>Panthera onca</t>
@@ -2666,7 +2669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q712"/>
+  <dimension ref="A1:Q713"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1">
@@ -34056,13 +34059,13 @@
         <v>0</v>
       </c>
       <c r="D593">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E593">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F593">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G593">
         <v>0</v>
@@ -34086,7 +34089,7 @@
         <v>50</v>
       </c>
       <c r="N593">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O593" t="s">
         <v>19</v>
@@ -34109,13 +34112,13 @@
         <v>0</v>
       </c>
       <c r="D594">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E594">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F594">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G594">
         <v>0</v>
@@ -34139,7 +34142,7 @@
         <v>50</v>
       </c>
       <c r="N594">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O594" t="s">
         <v>19</v>
@@ -34148,7 +34151,7 @@
         <v>20</v>
       </c>
       <c r="Q594" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="595" spans="1:17">
@@ -34159,13 +34162,13 @@
         <v>648</v>
       </c>
       <c r="C595">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D595">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E595">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F595">
         <v>0</v>
@@ -34192,13 +34195,13 @@
         <v>50</v>
       </c>
       <c r="N595">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O595" t="s">
         <v>19</v>
       </c>
       <c r="P595" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q595" t="s">
         <v>21</v>
@@ -34212,19 +34215,19 @@
         <v>649</v>
       </c>
       <c r="C596">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D596">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E596">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F596">
         <v>0</v>
       </c>
       <c r="G596">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H596">
         <v>0</v>
@@ -34242,19 +34245,19 @@
         <v>0</v>
       </c>
       <c r="M596" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="N596">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O596" t="s">
         <v>19</v>
       </c>
       <c r="P596" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q596" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="597" spans="1:17">
@@ -34265,7 +34268,7 @@
         <v>650</v>
       </c>
       <c r="C597">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D597">
         <v>0</v>
@@ -34277,13 +34280,13 @@
         <v>0</v>
       </c>
       <c r="G597">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H597">
         <v>0</v>
       </c>
       <c r="I597">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J597">
         <v>0</v>
@@ -34298,7 +34301,7 @@
         <v>18</v>
       </c>
       <c r="N597">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O597" t="s">
         <v>19</v>
@@ -34318,19 +34321,19 @@
         <v>651</v>
       </c>
       <c r="C598">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D598">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E598">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F598">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G598">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H598">
         <v>0</v>
@@ -34351,7 +34354,7 @@
         <v>18</v>
       </c>
       <c r="N598">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O598" t="s">
         <v>19</v>
@@ -34360,7 +34363,7 @@
         <v>20</v>
       </c>
       <c r="Q598" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="599" spans="1:17">
@@ -34371,25 +34374,25 @@
         <v>652</v>
       </c>
       <c r="C599">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D599">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E599">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F599">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G599">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H599">
         <v>0</v>
       </c>
       <c r="I599">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J599">
         <v>0</v>
@@ -34404,7 +34407,7 @@
         <v>18</v>
       </c>
       <c r="N599">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O599" t="s">
         <v>19</v>
@@ -34413,7 +34416,7 @@
         <v>20</v>
       </c>
       <c r="Q599" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="600" spans="1:17">
@@ -34424,7 +34427,7 @@
         <v>653</v>
       </c>
       <c r="C600">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D600">
         <v>0</v>
@@ -34451,13 +34454,13 @@
         <v>0</v>
       </c>
       <c r="L600">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M600" t="s">
         <v>18</v>
       </c>
       <c r="N600">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O600" t="s">
         <v>19</v>
@@ -34477,10 +34480,10 @@
         <v>654</v>
       </c>
       <c r="C601">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D601">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E601">
         <v>0</v>
@@ -34489,7 +34492,7 @@
         <v>0</v>
       </c>
       <c r="G601">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H601">
         <v>0</v>
@@ -34504,13 +34507,13 @@
         <v>0</v>
       </c>
       <c r="L601">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M601" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="N601">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O601" t="s">
         <v>19</v>
@@ -34519,7 +34522,7 @@
         <v>20</v>
       </c>
       <c r="Q601" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="602" spans="1:17">
@@ -34530,10 +34533,10 @@
         <v>655</v>
       </c>
       <c r="C602">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D602">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E602">
         <v>0</v>
@@ -34545,10 +34548,10 @@
         <v>0</v>
       </c>
       <c r="H602">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I602">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J602">
         <v>0</v>
@@ -34560,10 +34563,10 @@
         <v>0</v>
       </c>
       <c r="M602" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N602">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O602" t="s">
         <v>19</v>
@@ -34583,23 +34586,23 @@
         <v>656</v>
       </c>
       <c r="C603">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D603">
+        <v>10</v>
+      </c>
+      <c r="E603">
+        <v>0</v>
+      </c>
+      <c r="F603">
+        <v>0</v>
+      </c>
+      <c r="G603">
+        <v>0</v>
+      </c>
+      <c r="H603">
         <v>70</v>
       </c>
-      <c r="E603">
-        <v>0</v>
-      </c>
-      <c r="F603">
-        <v>0</v>
-      </c>
-      <c r="G603">
-        <v>0</v>
-      </c>
-      <c r="H603">
-        <v>0</v>
-      </c>
       <c r="I603">
         <v>10</v>
       </c>
@@ -34613,10 +34616,10 @@
         <v>0</v>
       </c>
       <c r="M603" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="N603">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O603" t="s">
         <v>19</v>
@@ -34639,22 +34642,22 @@
         <v>20</v>
       </c>
       <c r="D604">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E604">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F604">
         <v>0</v>
       </c>
       <c r="G604">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H604">
         <v>0</v>
       </c>
       <c r="I604">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J604">
         <v>0</v>
@@ -34663,13 +34666,13 @@
         <v>0</v>
       </c>
       <c r="L604">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M604" t="s">
         <v>50</v>
       </c>
       <c r="N604">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O604" t="s">
         <v>19</v>
@@ -34689,22 +34692,22 @@
         <v>658</v>
       </c>
       <c r="C605">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D605">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E605">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F605">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G605">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H605">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I605">
         <v>0</v>
@@ -34716,13 +34719,13 @@
         <v>0</v>
       </c>
       <c r="L605">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M605" t="s">
         <v>50</v>
       </c>
       <c r="N605">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O605" t="s">
         <v>19</v>
@@ -34731,7 +34734,7 @@
         <v>20</v>
       </c>
       <c r="Q605" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="606" spans="1:17">
@@ -34742,10 +34745,10 @@
         <v>659</v>
       </c>
       <c r="C606">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D606">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E606">
         <v>0</v>
@@ -34757,7 +34760,7 @@
         <v>0</v>
       </c>
       <c r="H606">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I606">
         <v>0</v>
@@ -34775,7 +34778,7 @@
         <v>50</v>
       </c>
       <c r="N606">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O606" t="s">
         <v>19</v>
@@ -34784,7 +34787,7 @@
         <v>20</v>
       </c>
       <c r="Q606" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="607" spans="1:17">
@@ -34798,19 +34801,19 @@
         <v>0</v>
       </c>
       <c r="D607">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E607">
         <v>0</v>
       </c>
       <c r="F607">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G607">
         <v>0</v>
       </c>
       <c r="H607">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I607">
         <v>0</v>
@@ -34828,7 +34831,7 @@
         <v>50</v>
       </c>
       <c r="N607">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O607" t="s">
         <v>19</v>
@@ -34890,7 +34893,7 @@
         <v>20</v>
       </c>
       <c r="Q608" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="609" spans="1:17">
@@ -34901,40 +34904,40 @@
         <v>662</v>
       </c>
       <c r="C609">
+        <v>0</v>
+      </c>
+      <c r="D609">
+        <v>100</v>
+      </c>
+      <c r="E609">
+        <v>0</v>
+      </c>
+      <c r="F609">
+        <v>0</v>
+      </c>
+      <c r="G609">
+        <v>0</v>
+      </c>
+      <c r="H609">
+        <v>0</v>
+      </c>
+      <c r="I609">
+        <v>0</v>
+      </c>
+      <c r="J609">
+        <v>0</v>
+      </c>
+      <c r="K609">
+        <v>0</v>
+      </c>
+      <c r="L609">
+        <v>0</v>
+      </c>
+      <c r="M609" t="s">
         <v>50</v>
       </c>
-      <c r="D609">
-        <v>20</v>
-      </c>
-      <c r="E609">
-        <v>0</v>
-      </c>
-      <c r="F609">
-        <v>0</v>
-      </c>
-      <c r="G609">
-        <v>10</v>
-      </c>
-      <c r="H609">
-        <v>0</v>
-      </c>
-      <c r="I609">
-        <v>0</v>
-      </c>
-      <c r="J609">
-        <v>0</v>
-      </c>
-      <c r="K609">
-        <v>0</v>
-      </c>
-      <c r="L609">
-        <v>20</v>
-      </c>
-      <c r="M609" t="s">
-        <v>18</v>
-      </c>
       <c r="N609">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O609" t="s">
         <v>19</v>
@@ -34943,7 +34946,7 @@
         <v>20</v>
       </c>
       <c r="Q609" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="610" spans="1:17">
@@ -34954,19 +34957,19 @@
         <v>663</v>
       </c>
       <c r="C610">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D610">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E610">
         <v>0</v>
       </c>
       <c r="F610">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G610">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H610">
         <v>0</v>
@@ -34981,19 +34984,19 @@
         <v>0</v>
       </c>
       <c r="L610">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M610" t="s">
         <v>18</v>
       </c>
       <c r="N610">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O610" t="s">
         <v>19</v>
       </c>
       <c r="P610" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Q610" t="s">
         <v>23</v>
@@ -35007,16 +35010,16 @@
         <v>664</v>
       </c>
       <c r="C611">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D611">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E611">
         <v>0</v>
       </c>
       <c r="F611">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G611">
         <v>0</v>
@@ -35037,10 +35040,10 @@
         <v>0</v>
       </c>
       <c r="M611" t="s">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="N611">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O611" t="s">
         <v>19</v>
@@ -35049,48 +35052,48 @@
         <v>171</v>
       </c>
       <c r="Q611" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="612" spans="1:17">
       <c r="A612" t="s">
+        <v>665</v>
+      </c>
+      <c r="B612" t="s">
+        <v>665</v>
+      </c>
+      <c r="C612">
+        <v>20</v>
+      </c>
+      <c r="D612">
+        <v>0</v>
+      </c>
+      <c r="E612">
+        <v>0</v>
+      </c>
+      <c r="F612">
+        <v>80</v>
+      </c>
+      <c r="G612">
+        <v>0</v>
+      </c>
+      <c r="H612">
+        <v>0</v>
+      </c>
+      <c r="I612">
+        <v>0</v>
+      </c>
+      <c r="J612">
+        <v>0</v>
+      </c>
+      <c r="K612">
+        <v>0</v>
+      </c>
+      <c r="L612">
+        <v>0</v>
+      </c>
+      <c r="M612" t="s">
         <v>666</v>
-      </c>
-      <c r="B612" t="s">
-        <v>666</v>
-      </c>
-      <c r="C612">
-        <v>60</v>
-      </c>
-      <c r="D612">
-        <v>0</v>
-      </c>
-      <c r="E612">
-        <v>0</v>
-      </c>
-      <c r="F612">
-        <v>40</v>
-      </c>
-      <c r="G612">
-        <v>0</v>
-      </c>
-      <c r="H612">
-        <v>0</v>
-      </c>
-      <c r="I612">
-        <v>0</v>
-      </c>
-      <c r="J612">
-        <v>0</v>
-      </c>
-      <c r="K612">
-        <v>0</v>
-      </c>
-      <c r="L612">
-        <v>0</v>
-      </c>
-      <c r="M612" t="s">
-        <v>18</v>
       </c>
       <c r="N612">
         <v>2</v>
@@ -35113,17 +35116,17 @@
         <v>667</v>
       </c>
       <c r="C613">
+        <v>60</v>
+      </c>
+      <c r="D613">
+        <v>0</v>
+      </c>
+      <c r="E613">
+        <v>0</v>
+      </c>
+      <c r="F613">
         <v>40</v>
       </c>
-      <c r="D613">
-        <v>0</v>
-      </c>
-      <c r="E613">
-        <v>0</v>
-      </c>
-      <c r="F613">
-        <v>60</v>
-      </c>
       <c r="G613">
         <v>0</v>
       </c>
@@ -35143,7 +35146,7 @@
         <v>0</v>
       </c>
       <c r="M613" t="s">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="N613">
         <v>2</v>
@@ -35166,7 +35169,7 @@
         <v>668</v>
       </c>
       <c r="C614">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D614">
         <v>0</v>
@@ -35175,7 +35178,7 @@
         <v>0</v>
       </c>
       <c r="F614">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G614">
         <v>0</v>
@@ -35196,7 +35199,7 @@
         <v>0</v>
       </c>
       <c r="M614" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N614">
         <v>2</v>
@@ -35249,7 +35252,7 @@
         <v>0</v>
       </c>
       <c r="M615" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N615">
         <v>2</v>
@@ -35272,19 +35275,19 @@
         <v>670</v>
       </c>
       <c r="C616">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D616">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E616">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F616">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G616">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H616">
         <v>0</v>
@@ -35302,19 +35305,19 @@
         <v>0</v>
       </c>
       <c r="M616" t="s">
-        <v>50</v>
+        <v>666</v>
       </c>
       <c r="N616">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O616" t="s">
         <v>19</v>
       </c>
       <c r="P616" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Q616" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="617" spans="1:17">
@@ -35328,16 +35331,16 @@
         <v>10</v>
       </c>
       <c r="D617">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E617">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F617">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G617">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H617">
         <v>0</v>
@@ -35367,7 +35370,7 @@
         <v>20</v>
       </c>
       <c r="Q617" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="618" spans="1:17">
@@ -35378,16 +35381,16 @@
         <v>672</v>
       </c>
       <c r="C618">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D618">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E618">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F618">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G618">
         <v>0</v>
@@ -35411,7 +35414,7 @@
         <v>50</v>
       </c>
       <c r="N618">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O618" t="s">
         <v>19</v>
@@ -35420,7 +35423,7 @@
         <v>20</v>
       </c>
       <c r="Q618" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="619" spans="1:17">
@@ -35487,7 +35490,7 @@
         <v>0</v>
       </c>
       <c r="D620">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E620">
         <v>0</v>
@@ -35502,7 +35505,7 @@
         <v>0</v>
       </c>
       <c r="I620">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J620">
         <v>0</v>
@@ -35517,7 +35520,7 @@
         <v>50</v>
       </c>
       <c r="N620">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O620" t="s">
         <v>19</v>
@@ -35526,7 +35529,7 @@
         <v>20</v>
       </c>
       <c r="Q620" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="621" spans="1:17">
@@ -35534,28 +35537,28 @@
         <v>675</v>
       </c>
       <c r="B621" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C621">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D621">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E621">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F621">
         <v>0</v>
       </c>
       <c r="G621">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H621">
         <v>0</v>
       </c>
       <c r="I621">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J621">
         <v>0</v>
@@ -35570,7 +35573,7 @@
         <v>50</v>
       </c>
       <c r="N621">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O621" t="s">
         <v>19</v>
@@ -35584,25 +35587,25 @@
     </row>
     <row r="622" spans="1:17">
       <c r="A622" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B622" t="s">
         <v>677</v>
       </c>
       <c r="C622">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D622">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E622">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F622">
         <v>0</v>
       </c>
       <c r="G622">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H622">
         <v>0</v>
@@ -35617,13 +35620,13 @@
         <v>0</v>
       </c>
       <c r="L622">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M622" t="s">
         <v>50</v>
       </c>
       <c r="N622">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O622" t="s">
         <v>19</v>
@@ -35632,7 +35635,7 @@
         <v>20</v>
       </c>
       <c r="Q622" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="623" spans="1:17">
@@ -35646,7 +35649,7 @@
         <v>0</v>
       </c>
       <c r="D623">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E623">
         <v>0</v>
@@ -35655,13 +35658,13 @@
         <v>0</v>
       </c>
       <c r="G623">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H623">
         <v>0</v>
       </c>
       <c r="I623">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J623">
         <v>0</v>
@@ -35670,19 +35673,19 @@
         <v>0</v>
       </c>
       <c r="L623">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M623" t="s">
         <v>50</v>
       </c>
       <c r="N623">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O623" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P623" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Q623" t="s">
         <v>21</v>
@@ -35696,13 +35699,13 @@
         <v>679</v>
       </c>
       <c r="C624">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D624">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E624">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F624">
         <v>0</v>
@@ -35714,31 +35717,31 @@
         <v>0</v>
       </c>
       <c r="I624">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J624">
         <v>0</v>
       </c>
       <c r="K624">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L624">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M624" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="N624">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O624" t="s">
         <v>38</v>
       </c>
       <c r="P624" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Q624" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="625" spans="1:17">
@@ -35746,19 +35749,19 @@
         <v>680</v>
       </c>
       <c r="B625" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C625">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D625">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E625">
         <v>20</v>
       </c>
       <c r="F625">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G625">
         <v>0</v>
@@ -35767,36 +35770,36 @@
         <v>0</v>
       </c>
       <c r="I625">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J625">
         <v>0</v>
       </c>
       <c r="K625">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L625">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M625" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="N625">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O625" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="P625" t="s">
         <v>20</v>
       </c>
       <c r="Q625" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="626" spans="1:17">
       <c r="A626" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B626" t="s">
         <v>682</v>
@@ -35805,13 +35808,13 @@
         <v>10</v>
       </c>
       <c r="D626">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E626">
         <v>20</v>
       </c>
       <c r="F626">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G626">
         <v>0</v>
@@ -35835,7 +35838,7 @@
         <v>50</v>
       </c>
       <c r="N626">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O626" t="s">
         <v>19</v>
@@ -35855,49 +35858,49 @@
         <v>683</v>
       </c>
       <c r="C627">
+        <v>10</v>
+      </c>
+      <c r="D627">
+        <v>70</v>
+      </c>
+      <c r="E627">
+        <v>20</v>
+      </c>
+      <c r="F627">
+        <v>0</v>
+      </c>
+      <c r="G627">
+        <v>0</v>
+      </c>
+      <c r="H627">
+        <v>0</v>
+      </c>
+      <c r="I627">
+        <v>0</v>
+      </c>
+      <c r="J627">
+        <v>0</v>
+      </c>
+      <c r="K627">
+        <v>0</v>
+      </c>
+      <c r="L627">
+        <v>0</v>
+      </c>
+      <c r="M627" t="s">
         <v>50</v>
       </c>
-      <c r="D627">
-        <v>0</v>
-      </c>
-      <c r="E627">
-        <v>0</v>
-      </c>
-      <c r="F627">
-        <v>50</v>
-      </c>
-      <c r="G627">
-        <v>0</v>
-      </c>
-      <c r="H627">
-        <v>0</v>
-      </c>
-      <c r="I627">
-        <v>0</v>
-      </c>
-      <c r="J627">
-        <v>0</v>
-      </c>
-      <c r="K627">
-        <v>0</v>
-      </c>
-      <c r="L627">
-        <v>0</v>
-      </c>
-      <c r="M627" t="s">
-        <v>18</v>
-      </c>
       <c r="N627">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O627" t="s">
         <v>19</v>
       </c>
       <c r="P627" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Q627" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="628" spans="1:17">
@@ -35908,16 +35911,16 @@
         <v>684</v>
       </c>
       <c r="C628">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D628">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E628">
         <v>0</v>
       </c>
       <c r="F628">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G628">
         <v>0</v>
@@ -35926,7 +35929,7 @@
         <v>0</v>
       </c>
       <c r="I628">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J628">
         <v>0</v>
@@ -35935,19 +35938,19 @@
         <v>0</v>
       </c>
       <c r="L628">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M628" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N628">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O628" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="P628" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Q628" t="s">
         <v>138</v>
@@ -35961,16 +35964,16 @@
         <v>685</v>
       </c>
       <c r="C629">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D629">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="E629">
         <v>0</v>
       </c>
       <c r="F629">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G629">
         <v>0</v>
@@ -35979,7 +35982,7 @@
         <v>0</v>
       </c>
       <c r="I629">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J629">
         <v>0</v>
@@ -35988,16 +35991,16 @@
         <v>0</v>
       </c>
       <c r="L629">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M629" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N629">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O629" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="P629" t="s">
         <v>20</v>
@@ -36014,16 +36017,16 @@
         <v>686</v>
       </c>
       <c r="C630">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D630">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E630">
         <v>0</v>
       </c>
       <c r="F630">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="G630">
         <v>0</v>
@@ -36044,7 +36047,7 @@
         <v>0</v>
       </c>
       <c r="M630" t="s">
-        <v>665</v>
+        <v>50</v>
       </c>
       <c r="N630">
         <v>2</v>
@@ -36053,10 +36056,10 @@
         <v>19</v>
       </c>
       <c r="P630" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Q630" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="631" spans="1:17">
@@ -36067,7 +36070,7 @@
         <v>687</v>
       </c>
       <c r="C631">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D631">
         <v>0</v>
@@ -36076,7 +36079,7 @@
         <v>0</v>
       </c>
       <c r="F631">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G631">
         <v>0</v>
@@ -36097,7 +36100,7 @@
         <v>0</v>
       </c>
       <c r="M631" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N631">
         <v>2</v>
@@ -36120,7 +36123,7 @@
         <v>688</v>
       </c>
       <c r="C632">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D632">
         <v>0</v>
@@ -36129,7 +36132,7 @@
         <v>0</v>
       </c>
       <c r="F632">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G632">
         <v>0</v>
@@ -36150,10 +36153,10 @@
         <v>0</v>
       </c>
       <c r="M632" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N632">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O632" t="s">
         <v>19</v>
@@ -36173,7 +36176,7 @@
         <v>689</v>
       </c>
       <c r="C633">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D633">
         <v>0</v>
@@ -36182,7 +36185,7 @@
         <v>0</v>
       </c>
       <c r="F633">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G633">
         <v>0</v>
@@ -36203,10 +36206,10 @@
         <v>0</v>
       </c>
       <c r="M633" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N633">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O633" t="s">
         <v>19</v>
@@ -36226,16 +36229,16 @@
         <v>690</v>
       </c>
       <c r="C634">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D634">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E634">
         <v>0</v>
       </c>
       <c r="F634">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G634">
         <v>0</v>
@@ -36244,28 +36247,28 @@
         <v>0</v>
       </c>
       <c r="I634">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J634">
         <v>0</v>
       </c>
       <c r="K634">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L634">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M634" t="s">
-        <v>50</v>
+        <v>666</v>
       </c>
       <c r="N634">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O634" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P634" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="Q634" t="s">
         <v>21</v>
@@ -36282,7 +36285,7 @@
         <v>20</v>
       </c>
       <c r="D635">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E635">
         <v>0</v>
@@ -36297,28 +36300,28 @@
         <v>0</v>
       </c>
       <c r="I635">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="J635">
         <v>0</v>
       </c>
       <c r="K635">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L635">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M635" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N635">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O635" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P635" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q635" t="s">
         <v>21</v>
@@ -36371,7 +36374,7 @@
         <v>26</v>
       </c>
       <c r="P636" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q636" t="s">
         <v>21</v>
@@ -36385,10 +36388,10 @@
         <v>693</v>
       </c>
       <c r="C637">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D637">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E637">
         <v>0</v>
@@ -36424,10 +36427,10 @@
         <v>26</v>
       </c>
       <c r="P637" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Q637" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="638" spans="1:17">
@@ -36494,7 +36497,7 @@
         <v>10</v>
       </c>
       <c r="D639">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E639">
         <v>0</v>
@@ -36503,13 +36506,13 @@
         <v>0</v>
       </c>
       <c r="G639">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H639">
         <v>0</v>
       </c>
       <c r="I639">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J639">
         <v>0</v>
@@ -36530,10 +36533,10 @@
         <v>26</v>
       </c>
       <c r="P639" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q639" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="640" spans="1:17">
@@ -36544,46 +36547,46 @@
         <v>696</v>
       </c>
       <c r="C640">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D640">
         <v>0</v>
       </c>
       <c r="E640">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F640">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G640">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H640">
         <v>0</v>
       </c>
       <c r="I640">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="J640">
         <v>0</v>
       </c>
       <c r="K640">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L640">
         <v>0</v>
       </c>
       <c r="M640" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="N640">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O640" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="P640" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q640" t="s">
         <v>21</v>
@@ -36597,16 +36600,16 @@
         <v>697</v>
       </c>
       <c r="C641">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D641">
         <v>0</v>
       </c>
       <c r="E641">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F641">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G641">
         <v>0</v>
@@ -36615,13 +36618,13 @@
         <v>0</v>
       </c>
       <c r="I641">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J641">
         <v>0</v>
       </c>
       <c r="K641">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L641">
         <v>0</v>
@@ -36630,10 +36633,10 @@
         <v>18</v>
       </c>
       <c r="N641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O641" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P641" t="s">
         <v>20</v>
@@ -36650,13 +36653,13 @@
         <v>698</v>
       </c>
       <c r="C642">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D642">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E642">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F642">
         <v>0</v>
@@ -36668,31 +36671,31 @@
         <v>0</v>
       </c>
       <c r="I642">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J642">
         <v>0</v>
       </c>
       <c r="K642">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L642">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M642" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N642">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O642" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P642" t="s">
         <v>20</v>
       </c>
       <c r="Q642" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="643" spans="1:17">
@@ -36700,13 +36703,13 @@
         <v>699</v>
       </c>
       <c r="B643" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C643">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D643">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E643">
         <v>0</v>
@@ -36721,22 +36724,22 @@
         <v>0</v>
       </c>
       <c r="I643">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J643">
         <v>0</v>
       </c>
       <c r="K643">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L643">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M643" t="s">
         <v>25</v>
       </c>
       <c r="N643">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O643" t="s">
         <v>26</v>
@@ -36750,7 +36753,7 @@
     </row>
     <row r="644" spans="1:17">
       <c r="A644" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B644" t="s">
         <v>701</v>
@@ -36803,7 +36806,7 @@
     </row>
     <row r="645" spans="1:17">
       <c r="A645" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B645" t="s">
         <v>702</v>
@@ -36957,7 +36960,7 @@
         <v>20</v>
       </c>
       <c r="Q647" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="648" spans="1:17">
@@ -36968,7 +36971,7 @@
         <v>705</v>
       </c>
       <c r="C648">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D648">
         <v>0</v>
@@ -36980,10 +36983,10 @@
         <v>0</v>
       </c>
       <c r="G648">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H648">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I648">
         <v>0</v>
@@ -36992,16 +36995,16 @@
         <v>0</v>
       </c>
       <c r="K648">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L648">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M648" t="s">
         <v>25</v>
       </c>
       <c r="N648">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O648" t="s">
         <v>26</v>
@@ -37027,25 +37030,25 @@
         <v>0</v>
       </c>
       <c r="E649">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F649">
         <v>0</v>
       </c>
       <c r="G649">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H649">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I649">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J649">
         <v>0</v>
       </c>
       <c r="K649">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L649">
         <v>60</v>
@@ -37054,7 +37057,7 @@
         <v>25</v>
       </c>
       <c r="N649">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O649" t="s">
         <v>26</v>
@@ -37074,13 +37077,13 @@
         <v>707</v>
       </c>
       <c r="C650">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D650">
         <v>0</v>
       </c>
       <c r="E650">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F650">
         <v>0</v>
@@ -37092,7 +37095,7 @@
         <v>0</v>
       </c>
       <c r="I650">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J650">
         <v>0</v>
@@ -37101,13 +37104,13 @@
         <v>0</v>
       </c>
       <c r="L650">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M650" t="s">
         <v>25</v>
       </c>
       <c r="N650">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O650" t="s">
         <v>26</v>
@@ -37116,7 +37119,7 @@
         <v>20</v>
       </c>
       <c r="Q650" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
     </row>
     <row r="651" spans="1:17">
@@ -37251,7 +37254,7 @@
         <v>0</v>
       </c>
       <c r="I653">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J653">
         <v>0</v>
@@ -37260,13 +37263,13 @@
         <v>0</v>
       </c>
       <c r="L653">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M653" t="s">
         <v>25</v>
       </c>
       <c r="N653">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O653" t="s">
         <v>26</v>
@@ -37275,7 +37278,7 @@
         <v>20</v>
       </c>
       <c r="Q653" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="654" spans="1:17">
@@ -37304,7 +37307,7 @@
         <v>0</v>
       </c>
       <c r="I654">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J654">
         <v>0</v>
@@ -37313,13 +37316,13 @@
         <v>0</v>
       </c>
       <c r="L654">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M654" t="s">
         <v>25</v>
       </c>
       <c r="N654">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O654" t="s">
         <v>26</v>
@@ -37328,7 +37331,7 @@
         <v>20</v>
       </c>
       <c r="Q654" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="655" spans="1:17">
@@ -37381,7 +37384,7 @@
         <v>20</v>
       </c>
       <c r="Q655" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="656" spans="1:17">
@@ -37434,7 +37437,7 @@
         <v>20</v>
       </c>
       <c r="Q656" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="657" spans="1:17">
@@ -37487,7 +37490,7 @@
         <v>20</v>
       </c>
       <c r="Q657" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="658" spans="1:17">
@@ -37540,7 +37543,7 @@
         <v>20</v>
       </c>
       <c r="Q658" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="659" spans="1:17">
@@ -37593,7 +37596,7 @@
         <v>20</v>
       </c>
       <c r="Q659" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="660" spans="1:17">
@@ -37646,7 +37649,7 @@
         <v>20</v>
       </c>
       <c r="Q660" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="661" spans="1:17">
@@ -37699,7 +37702,7 @@
         <v>20</v>
       </c>
       <c r="Q661" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="662" spans="1:17">
@@ -37781,7 +37784,7 @@
         <v>0</v>
       </c>
       <c r="I663">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J663">
         <v>0</v>
@@ -37790,13 +37793,13 @@
         <v>0</v>
       </c>
       <c r="L663">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M663" t="s">
         <v>25</v>
       </c>
       <c r="N663">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O663" t="s">
         <v>26</v>
@@ -37834,7 +37837,7 @@
         <v>0</v>
       </c>
       <c r="I664">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J664">
         <v>0</v>
@@ -37843,13 +37846,13 @@
         <v>0</v>
       </c>
       <c r="L664">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M664" t="s">
         <v>25</v>
       </c>
       <c r="N664">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O664" t="s">
         <v>26</v>
@@ -37858,7 +37861,7 @@
         <v>20</v>
       </c>
       <c r="Q664" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="665" spans="1:17">
@@ -37881,13 +37884,13 @@
         <v>0</v>
       </c>
       <c r="G665">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H665">
         <v>0</v>
       </c>
       <c r="I665">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J665">
         <v>0</v>
@@ -37896,13 +37899,13 @@
         <v>0</v>
       </c>
       <c r="L665">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M665" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="N665">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O665" t="s">
         <v>26</v>
@@ -37911,7 +37914,7 @@
         <v>20</v>
       </c>
       <c r="Q665" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="666" spans="1:17">
@@ -37934,13 +37937,13 @@
         <v>0</v>
       </c>
       <c r="G666">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H666">
         <v>0</v>
       </c>
       <c r="I666">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J666">
         <v>0</v>
@@ -37949,13 +37952,13 @@
         <v>0</v>
       </c>
       <c r="L666">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M666" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="N666">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O666" t="s">
         <v>26</v>
@@ -38017,7 +38020,7 @@
         <v>20</v>
       </c>
       <c r="Q667" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="668" spans="1:17">
@@ -38052,16 +38055,16 @@
         <v>0</v>
       </c>
       <c r="K668">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L668">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M668" t="s">
         <v>25</v>
       </c>
       <c r="N668">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O668" t="s">
         <v>26</v>
@@ -38070,7 +38073,7 @@
         <v>20</v>
       </c>
       <c r="Q668" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="669" spans="1:17">
@@ -38099,7 +38102,7 @@
         <v>0</v>
       </c>
       <c r="I669">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J669">
         <v>0</v>
@@ -38108,13 +38111,13 @@
         <v>10</v>
       </c>
       <c r="L669">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M669" t="s">
         <v>25</v>
       </c>
       <c r="N669">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O669" t="s">
         <v>26</v>
@@ -38123,7 +38126,7 @@
         <v>20</v>
       </c>
       <c r="Q669" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="670" spans="1:17">
@@ -38152,22 +38155,22 @@
         <v>0</v>
       </c>
       <c r="I670">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J670">
         <v>0</v>
       </c>
       <c r="K670">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L670">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M670" t="s">
         <v>25</v>
       </c>
       <c r="N670">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O670" t="s">
         <v>26</v>
@@ -38176,7 +38179,7 @@
         <v>20</v>
       </c>
       <c r="Q670" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="671" spans="1:17">
@@ -38205,7 +38208,7 @@
         <v>0</v>
       </c>
       <c r="I671">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J671">
         <v>0</v>
@@ -38214,13 +38217,13 @@
         <v>0</v>
       </c>
       <c r="L671">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M671" t="s">
         <v>25</v>
       </c>
       <c r="N671">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O671" t="s">
         <v>26</v>
@@ -38229,7 +38232,7 @@
         <v>20</v>
       </c>
       <c r="Q671" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="672" spans="1:17">
@@ -38258,7 +38261,7 @@
         <v>0</v>
       </c>
       <c r="I672">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J672">
         <v>0</v>
@@ -38267,13 +38270,13 @@
         <v>0</v>
       </c>
       <c r="L672">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M672" t="s">
         <v>25</v>
       </c>
       <c r="N672">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O672" t="s">
         <v>26</v>
@@ -38346,49 +38349,49 @@
         <v>731</v>
       </c>
       <c r="C674">
+        <v>0</v>
+      </c>
+      <c r="D674">
+        <v>0</v>
+      </c>
+      <c r="E674">
+        <v>0</v>
+      </c>
+      <c r="F674">
+        <v>0</v>
+      </c>
+      <c r="G674">
+        <v>0</v>
+      </c>
+      <c r="H674">
+        <v>0</v>
+      </c>
+      <c r="I674">
+        <v>0</v>
+      </c>
+      <c r="J674">
+        <v>0</v>
+      </c>
+      <c r="K674">
+        <v>0</v>
+      </c>
+      <c r="L674">
         <v>100</v>
       </c>
-      <c r="D674">
-        <v>0</v>
-      </c>
-      <c r="E674">
-        <v>0</v>
-      </c>
-      <c r="F674">
-        <v>0</v>
-      </c>
-      <c r="G674">
-        <v>0</v>
-      </c>
-      <c r="H674">
-        <v>0</v>
-      </c>
-      <c r="I674">
-        <v>0</v>
-      </c>
-      <c r="J674">
-        <v>0</v>
-      </c>
-      <c r="K674">
-        <v>0</v>
-      </c>
-      <c r="L674">
-        <v>0</v>
-      </c>
       <c r="M674" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N674">
         <v>1</v>
       </c>
       <c r="O674" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="P674" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Q674" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="675" spans="1:17">
@@ -38399,7 +38402,7 @@
         <v>732</v>
       </c>
       <c r="C675">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D675">
         <v>0</v>
@@ -38408,7 +38411,7 @@
         <v>0</v>
       </c>
       <c r="F675">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G675">
         <v>0</v>
@@ -38432,7 +38435,7 @@
         <v>18</v>
       </c>
       <c r="N675">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O675" t="s">
         <v>19</v>
@@ -38441,7 +38444,7 @@
         <v>171</v>
       </c>
       <c r="Q675" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="676" spans="1:17">
@@ -38505,7 +38508,7 @@
         <v>734</v>
       </c>
       <c r="C677">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D677">
         <v>0</v>
@@ -38514,7 +38517,7 @@
         <v>0</v>
       </c>
       <c r="F677">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G677">
         <v>0</v>
@@ -38558,7 +38561,7 @@
         <v>735</v>
       </c>
       <c r="C678">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D678">
         <v>0</v>
@@ -38567,7 +38570,7 @@
         <v>0</v>
       </c>
       <c r="F678">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G678">
         <v>0</v>
@@ -38591,7 +38594,7 @@
         <v>18</v>
       </c>
       <c r="N678">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O678" t="s">
         <v>19</v>
@@ -38611,7 +38614,7 @@
         <v>736</v>
       </c>
       <c r="C679">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D679">
         <v>0</v>
@@ -38620,7 +38623,7 @@
         <v>0</v>
       </c>
       <c r="F679">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G679">
         <v>0</v>
@@ -38644,7 +38647,7 @@
         <v>18</v>
       </c>
       <c r="N679">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O679" t="s">
         <v>19</v>
@@ -38664,7 +38667,7 @@
         <v>737</v>
       </c>
       <c r="C680">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D680">
         <v>0</v>
@@ -38673,7 +38676,7 @@
         <v>0</v>
       </c>
       <c r="F680">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G680">
         <v>0</v>
@@ -38717,7 +38720,7 @@
         <v>738</v>
       </c>
       <c r="C681">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D681">
         <v>0</v>
@@ -38726,7 +38729,7 @@
         <v>0</v>
       </c>
       <c r="F681">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G681">
         <v>0</v>
@@ -38747,7 +38750,7 @@
         <v>0</v>
       </c>
       <c r="M681" t="s">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="N681">
         <v>2</v>
@@ -38770,7 +38773,7 @@
         <v>739</v>
       </c>
       <c r="C682">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="D682">
         <v>0</v>
@@ -38779,7 +38782,7 @@
         <v>0</v>
       </c>
       <c r="F682">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="G682">
         <v>0</v>
@@ -38800,7 +38803,7 @@
         <v>0</v>
       </c>
       <c r="M682" t="s">
-        <v>18</v>
+        <v>666</v>
       </c>
       <c r="N682">
         <v>2</v>
@@ -38812,7 +38815,7 @@
         <v>171</v>
       </c>
       <c r="Q682" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
     </row>
     <row r="683" spans="1:17">
@@ -38876,7 +38879,7 @@
         <v>741</v>
       </c>
       <c r="C684">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D684">
         <v>0</v>
@@ -38885,7 +38888,7 @@
         <v>0</v>
       </c>
       <c r="F684">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G684">
         <v>0</v>
@@ -38929,7 +38932,7 @@
         <v>742</v>
       </c>
       <c r="C685">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D685">
         <v>0</v>
@@ -38938,7 +38941,7 @@
         <v>0</v>
       </c>
       <c r="F685">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G685">
         <v>0</v>
@@ -38959,7 +38962,7 @@
         <v>0</v>
       </c>
       <c r="M685" t="s">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="N685">
         <v>2</v>
@@ -38971,7 +38974,7 @@
         <v>171</v>
       </c>
       <c r="Q685" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="686" spans="1:17">
@@ -39012,7 +39015,7 @@
         <v>0</v>
       </c>
       <c r="M686" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N686">
         <v>2</v>
@@ -39065,7 +39068,7 @@
         <v>0</v>
       </c>
       <c r="M687" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N687">
         <v>2</v>
@@ -39088,16 +39091,16 @@
         <v>745</v>
       </c>
       <c r="C688">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D688">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E688">
         <v>0</v>
       </c>
       <c r="F688">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G688">
         <v>0</v>
@@ -39118,10 +39121,10 @@
         <v>0</v>
       </c>
       <c r="M688" t="s">
-        <v>50</v>
+        <v>666</v>
       </c>
       <c r="N688">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O688" t="s">
         <v>19</v>
@@ -39141,16 +39144,16 @@
         <v>746</v>
       </c>
       <c r="C689">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D689">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E689">
         <v>0</v>
       </c>
       <c r="F689">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G689">
         <v>0</v>
@@ -39171,7 +39174,7 @@
         <v>0</v>
       </c>
       <c r="M689" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="N689">
         <v>3</v>
@@ -39194,16 +39197,16 @@
         <v>747</v>
       </c>
       <c r="C690">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D690">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E690">
         <v>0</v>
       </c>
       <c r="F690">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G690">
         <v>0</v>
@@ -39224,10 +39227,10 @@
         <v>0</v>
       </c>
       <c r="M690" t="s">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="N690">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O690" t="s">
         <v>19</v>
@@ -39236,7 +39239,7 @@
         <v>171</v>
       </c>
       <c r="Q690" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="691" spans="1:17">
@@ -39247,7 +39250,7 @@
         <v>748</v>
       </c>
       <c r="C691">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D691">
         <v>0</v>
@@ -39256,7 +39259,7 @@
         <v>0</v>
       </c>
       <c r="F691">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G691">
         <v>0</v>
@@ -39277,7 +39280,7 @@
         <v>0</v>
       </c>
       <c r="M691" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N691">
         <v>2</v>
@@ -39289,7 +39292,7 @@
         <v>171</v>
       </c>
       <c r="Q691" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="692" spans="1:17">
@@ -39300,17 +39303,17 @@
         <v>749</v>
       </c>
       <c r="C692">
+        <v>40</v>
+      </c>
+      <c r="D692">
+        <v>0</v>
+      </c>
+      <c r="E692">
+        <v>0</v>
+      </c>
+      <c r="F692">
         <v>60</v>
       </c>
-      <c r="D692">
-        <v>0</v>
-      </c>
-      <c r="E692">
-        <v>0</v>
-      </c>
-      <c r="F692">
-        <v>40</v>
-      </c>
       <c r="G692">
         <v>0</v>
       </c>
@@ -39330,7 +39333,7 @@
         <v>0</v>
       </c>
       <c r="M692" t="s">
-        <v>18</v>
+        <v>666</v>
       </c>
       <c r="N692">
         <v>2</v>
@@ -39459,7 +39462,7 @@
         <v>752</v>
       </c>
       <c r="C695">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D695">
         <v>0</v>
@@ -39468,7 +39471,7 @@
         <v>0</v>
       </c>
       <c r="F695">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G695">
         <v>0</v>
@@ -39489,7 +39492,7 @@
         <v>0</v>
       </c>
       <c r="M695" t="s">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="N695">
         <v>2</v>
@@ -39501,7 +39504,7 @@
         <v>171</v>
       </c>
       <c r="Q695" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="696" spans="1:17">
@@ -39542,7 +39545,7 @@
         <v>0</v>
       </c>
       <c r="M696" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N696">
         <v>2</v>
@@ -39565,7 +39568,7 @@
         <v>754</v>
       </c>
       <c r="C697">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D697">
         <v>0</v>
@@ -39574,7 +39577,7 @@
         <v>0</v>
       </c>
       <c r="F697">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G697">
         <v>0</v>
@@ -39595,7 +39598,7 @@
         <v>0</v>
       </c>
       <c r="M697" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N697">
         <v>2</v>
@@ -39607,7 +39610,7 @@
         <v>171</v>
       </c>
       <c r="Q697" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
     </row>
     <row r="698" spans="1:17">
@@ -39648,7 +39651,7 @@
         <v>0</v>
       </c>
       <c r="M698" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N698">
         <v>2</v>
@@ -39701,7 +39704,7 @@
         <v>0</v>
       </c>
       <c r="M699" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N699">
         <v>2</v>
@@ -39724,7 +39727,7 @@
         <v>757</v>
       </c>
       <c r="C700">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D700">
         <v>0</v>
@@ -39733,7 +39736,7 @@
         <v>0</v>
       </c>
       <c r="F700">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G700">
         <v>0</v>
@@ -39754,10 +39757,10 @@
         <v>0</v>
       </c>
       <c r="M700" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N700">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O700" t="s">
         <v>19</v>
@@ -39777,7 +39780,7 @@
         <v>758</v>
       </c>
       <c r="C701">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D701">
         <v>0</v>
@@ -39786,7 +39789,7 @@
         <v>0</v>
       </c>
       <c r="F701">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G701">
         <v>0</v>
@@ -39807,10 +39810,10 @@
         <v>0</v>
       </c>
       <c r="M701" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N701">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O701" t="s">
         <v>19</v>
@@ -39830,7 +39833,7 @@
         <v>759</v>
       </c>
       <c r="C702">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="D702">
         <v>0</v>
@@ -39839,7 +39842,7 @@
         <v>0</v>
       </c>
       <c r="F702">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G702">
         <v>0</v>
@@ -39860,7 +39863,7 @@
         <v>0</v>
       </c>
       <c r="M702" t="s">
-        <v>18</v>
+        <v>666</v>
       </c>
       <c r="N702">
         <v>2</v>
@@ -40042,7 +40045,7 @@
         <v>763</v>
       </c>
       <c r="C706">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D706">
         <v>0</v>
@@ -40051,7 +40054,7 @@
         <v>0</v>
       </c>
       <c r="F706">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G706">
         <v>0</v>
@@ -40075,7 +40078,7 @@
         <v>18</v>
       </c>
       <c r="N706">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O706" t="s">
         <v>19</v>
@@ -40148,7 +40151,7 @@
         <v>765</v>
       </c>
       <c r="C708">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D708">
         <v>0</v>
@@ -40157,7 +40160,7 @@
         <v>0</v>
       </c>
       <c r="F708">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G708">
         <v>0</v>
@@ -40181,7 +40184,7 @@
         <v>18</v>
       </c>
       <c r="N708">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O708" t="s">
         <v>19</v>
@@ -40254,7 +40257,7 @@
         <v>767</v>
       </c>
       <c r="C710">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D710">
         <v>0</v>
@@ -40263,7 +40266,7 @@
         <v>0</v>
       </c>
       <c r="F710">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="G710">
         <v>0</v>
@@ -40284,7 +40287,7 @@
         <v>0</v>
       </c>
       <c r="M710" t="s">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="N710">
         <v>2</v>
@@ -40296,7 +40299,7 @@
         <v>171</v>
       </c>
       <c r="Q710" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
     </row>
     <row r="711" spans="1:17">
@@ -40307,7 +40310,7 @@
         <v>768</v>
       </c>
       <c r="C711">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D711">
         <v>0</v>
@@ -40316,7 +40319,7 @@
         <v>0</v>
       </c>
       <c r="F711">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G711">
         <v>0</v>
@@ -40337,10 +40340,10 @@
         <v>0</v>
       </c>
       <c r="M711" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N711">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O711" t="s">
         <v>19</v>
@@ -40360,7 +40363,7 @@
         <v>769</v>
       </c>
       <c r="C712">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D712">
         <v>0</v>
@@ -40369,7 +40372,7 @@
         <v>0</v>
       </c>
       <c r="F712">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G712">
         <v>0</v>
@@ -40390,10 +40393,10 @@
         <v>0</v>
       </c>
       <c r="M712" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N712">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O712" t="s">
         <v>19</v>
@@ -40402,297 +40405,63 @@
         <v>171</v>
       </c>
       <c r="Q712" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="713" spans="1:17">
+      <c r="A713" t="s">
+        <v>770</v>
+      </c>
+      <c r="B713" t="s">
+        <v>770</v>
+      </c>
+      <c r="C713">
+        <v>40</v>
+      </c>
+      <c r="D713">
+        <v>0</v>
+      </c>
+      <c r="E713">
+        <v>0</v>
+      </c>
+      <c r="F713">
+        <v>60</v>
+      </c>
+      <c r="G713">
+        <v>0</v>
+      </c>
+      <c r="H713">
+        <v>0</v>
+      </c>
+      <c r="I713">
+        <v>0</v>
+      </c>
+      <c r="J713">
+        <v>0</v>
+      </c>
+      <c r="K713">
+        <v>0</v>
+      </c>
+      <c r="L713">
+        <v>0</v>
+      </c>
+      <c r="M713" t="s">
+        <v>666</v>
+      </c>
+      <c r="N713">
+        <v>2</v>
+      </c>
+      <c r="O713" t="s">
+        <v>19</v>
+      </c>
+      <c r="P713" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q713" t="s">
         <v>138</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD173B35-9274-4C66-B95B-E33D16B66E1E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5E6638D-6FD1-41BB-BA35-3B1688C1E326}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{560E6CB0-4BB4-4898-8A8E-80E3AEE72D42}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -40464,4 +40464,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB6E221E-B973-4BF3-82A3-D87E9598FCE5}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C186F49-06B4-483E-A0DD-A3B709DAF9F8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDEAB0C3-982F-4BB4-B2EC-10F1C6B1F50D}"/>
 </file>